--- a/Databases/Database3/Output/2014/db3_2014_FINAL.xlsx
+++ b/Databases/Database3/Output/2014/db3_2014_FINAL.xlsx
@@ -4019,7 +4019,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-31 11:38</t>
+          <t>2026-04-14 13:55</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Route, Latitude, Longitude, SurveyDate, TotalObserved, FlagCode</t>
+          <t>Route, Latitude, Longitude, SurveyDate, TotalObserved, FlagCode, FlagColor, BandCombo</t>
         </is>
       </c>
     </row>
